--- a/artfynd/A 9527-2024 artfynd.xlsx
+++ b/artfynd/A 9527-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136045528</v>
       </c>
       <c r="B2" t="n">
-        <v>58232</v>
+        <v>58233</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 9527-2024 artfynd.xlsx
+++ b/artfynd/A 9527-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136045528</v>
       </c>
       <c r="B2" t="n">
-        <v>58233</v>
+        <v>58237</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 9527-2024 artfynd.xlsx
+++ b/artfynd/A 9527-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136045528</v>
       </c>
       <c r="B2" t="n">
-        <v>58237</v>
+        <v>58238</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 9527-2024 artfynd.xlsx
+++ b/artfynd/A 9527-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136045528</v>
       </c>
       <c r="B2" t="n">
-        <v>58238</v>
+        <v>58243</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 9527-2024 artfynd.xlsx
+++ b/artfynd/A 9527-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136045528</v>
       </c>
       <c r="B2" t="n">
-        <v>58243</v>
+        <v>58256</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
